--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_131_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_131_R14.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3142</v>
+        <v>14.0294</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2979</v>
+        <v>12.0803</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0163</v>
+        <v>1.9491</v>
       </c>
       <c r="G2" t="n">
         <v>8.932</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3163</v>
+        <v>0.3989</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9709</v>
+        <v>-0.1885</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6546</v>
+        <v>0.5874</v>
       </c>
       <c r="V2" t="n">
         <v>3.0748</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9546</v>
+        <v>6.2571</v>
       </c>
       <c r="E3" t="n">
         <v>7.4085</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4539</v>
+        <v>-1.1514</v>
       </c>
       <c r="G3" t="n">
         <v>6.9256</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8112</v>
+        <v>-1.5088</v>
       </c>
       <c r="T3" t="n">
         <v>-0.5149</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2964</v>
+        <v>-0.9939</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3936</v>
+        <v>3.2927</v>
       </c>
       <c r="E4" t="n">
         <v>3.9536</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5601</v>
+        <v>-0.6609</v>
       </c>
       <c r="G4" t="n">
         <v>1.3919</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7121</v>
+        <v>-0.8129</v>
       </c>
       <c r="T4" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1893</v>
+        <v>-0.2902</v>
       </c>
       <c r="V4" t="n">
         <v>0.3943</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1849</v>
+        <v>2.0661</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0758</v>
+        <v>1.8428</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1091</v>
+        <v>0.2232</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0594</v>
+        <v>1.3083</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8415</v>
+        <v>1.5426</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9009</v>
+        <v>-0.2343</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4438</v>
+        <v>2.0983</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9817</v>
+        <v>1.5965</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4255</v>
+        <v>0.5018</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6156</v>
+        <v>-0.79</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1401</v>
+        <v>-0.0539</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4755</v>
+        <v>-0.7361</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3344</v>
+        <v>-0.402</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7695</v>
+        <v>-0.2555</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5649</v>
+        <v>-0.1465</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8473</v>
+        <v>1.3393</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7249</v>
+        <v>0.1269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1224</v>
+        <v>1.2124</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3083</v>
+        <v>-1.0046</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5426</v>
+        <v>-0.9411</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2343</v>
+        <v>-0.0636</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0983</v>
+        <v>-0.5719</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5965</v>
+        <v>-0.7191</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5018</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.79</v>
+        <v>-0.4327</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0539</v>
+        <v>-0.222</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7361</v>
+        <v>-0.2108</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6207</v>
+        <v>-0.5838</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2473</v>
+        <v>-0.2104</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4065</v>
+        <v>1.2124</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1269</v>
+        <v>2.789</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2797</v>
+        <v>-1.5766</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0046</v>
+        <v>2.7935</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9411</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0636</v>
+        <v>1.8404</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5719</v>
+        <v>5.9676</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7191</v>
+        <v>1.8086</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>4.159</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4327</v>
+        <v>-3.1741</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.222</v>
+        <v>-0.8555</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2108</v>
+        <v>-2.3186</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.9432</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5165999999999999</v>
+        <v>0.2023</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.0868</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1432</v>
+        <v>0.1155</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7731</v>
+        <v>0.9963</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2418</v>
+        <v>1.0889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5314</v>
+        <v>-0.0926</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7814</v>
+        <v>-2.0594</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.8415</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7465</v>
+        <v>-2.9009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5911</v>
+        <v>-0.4438</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2303</v>
+        <v>0.9817</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>-1.4255</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3725</v>
+        <v>-1.6156</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2651</v>
+        <v>-0.1401</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1074</v>
+        <v>-1.4755</v>
       </c>
       <c r="P8" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.4639</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-1.6237</v>
       </c>
       <c r="R8" t="n">
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6241</v>
+        <v>1.1459</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1325</v>
+        <v>0.7826</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4916</v>
+        <v>0.3633</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.317</v>
+        <v>0.4768</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.1554</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.6322</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6464</v>
+        <v>-0.7814</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.539</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="I9" t="n">
+        <v>-1.7465</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5911</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.2303</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.6391</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.3725</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.2651</v>
+      </c>
+      <c r="O9" t="n">
         <v>-1.1074</v>
       </c>
-      <c r="J9" t="n">
-        <v>-0.1238</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.0736</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.0502</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-1.5226</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.4655</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.0572</v>
-      </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5149</v>
+        <v>1.3278</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1968</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3181</v>
+        <v>0.5924</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1444</v>
+        <v>0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2448</v>
+        <v>0.3916</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8887</v>
+        <v>-0.4913</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6439</v>
+        <v>0.883</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7935</v>
+        <v>-1.6464</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9530999999999999</v>
+        <v>-0.539</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8404</v>
+        <v>-1.1074</v>
       </c>
       <c r="J10" t="n">
-        <v>5.9676</v>
+        <v>-0.1238</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8086</v>
+        <v>-0.0736</v>
       </c>
       <c r="L10" t="n">
-        <v>4.159</v>
+        <v>-0.0502</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1741</v>
+        <v>-1.5226</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8555</v>
+        <v>-0.4655</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3186</v>
+        <v>-1.0572</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3195</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9432</v>
+        <v>-2.7834</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7653</v>
+        <v>0.5895</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8136</v>
+        <v>0.2715</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0483</v>
+        <v>0.3181</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5977</v>
+        <v>-0.8843</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1433</v>
+        <v>1.7894</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7409</v>
+        <v>-2.6737</v>
       </c>
       <c r="G11" t="n">
         <v>0.1902</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1942</v>
+        <v>-0.0925</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2934</v>
+        <v>-0.2262</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1928</v>
+        <v>-2.3437</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.0474</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1223</v>
+        <v>-2.3912</v>
       </c>
       <c r="G12" t="n">
         <v>0.0467</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3839</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0105</v>
+        <v>-0.2794</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8389</v>
+        <v>-2.6538</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.558</v>
+        <v>-2.4401</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2809</v>
+        <v>-0.2137</v>
       </c>
       <c r="G13" t="n">
         <v>-0.407</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1125</v>
+        <v>0.0727</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.8066</v>
+        <v>24.1799</v>
       </c>
       <c r="E14" t="n">
-        <v>27.6669</v>
+        <v>28.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.860099999999999</v>
+        <v>-3.860200000000001</v>
       </c>
       <c r="G14" t="n">
         <v>15.6894</v>
@@ -1516,7 +1516,7 @@
         <v>7.809600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>7.879900000000003</v>
+        <v>7.879900000000001</v>
       </c>
       <c r="J14" t="n">
         <v>34.2045</v>
@@ -1537,7 +1537,7 @@
         <v>-14.7548</v>
       </c>
       <c r="P14" t="n">
-        <v>9.999999999932285e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.3964</v>
@@ -1546,16 +1546,16 @@
         <v>17.3966</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5709999999999996</v>
+        <v>-0.1976999999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4306999999999997</v>
+        <v>-0.05719999999999995</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1404000000000001</v>
+        <v>-0.1404999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>8.688299999999998</v>
+        <v>8.6883</v>
       </c>
       <c r="W14" t="n">
         <v>11.2892</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8204</v>
+        <v>3.1806</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3801</v>
+        <v>4.9083</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5597</v>
+        <v>-1.7277</v>
       </c>
       <c r="G15" t="n">
         <v>1.8395</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.981</v>
+        <v>0.3411</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6018</v>
+        <v>0.13</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3791</v>
+        <v>0.2111</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9892</v>
+        <v>1.6126</v>
       </c>
       <c r="E16" t="n">
-        <v>2.827</v>
+        <v>3.4168</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8378</v>
+        <v>-1.8042</v>
       </c>
       <c r="G16" t="n">
         <v>2.376</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1215</v>
+        <v>-0.4982</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V16" t="n">
         <v>2.2862</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7851</v>
+        <v>1.5994</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2877</v>
+        <v>2.3666</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5026</v>
+        <v>-0.7672</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7183</v>
+        <v>0.1132</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0048</v>
+        <v>-0.3887</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7231</v>
+        <v>0.502</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2625</v>
+        <v>2.7044</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9312</v>
+        <v>0.2017</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3312</v>
+        <v>2.5027</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9808</v>
+        <v>-2.5912</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9265</v>
+        <v>-0.5904</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0543</v>
+        <v>-2.0008</v>
       </c>
       <c r="P17" t="n">
         <v>1.6237</v>
@@ -1780,28 +1780,28 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>3.0241</v>
+        <v>-0.1375</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0252</v>
+        <v>-0.3378</v>
       </c>
       <c r="U17" t="n">
-        <v>0.999</v>
+        <v>0.2003</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>-0.7279</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6589</v>
+        <v>1.3056</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0589</v>
+        <v>-2.0335</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1132</v>
+        <v>-1.4884</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3887</v>
+        <v>0.4154</v>
       </c>
       <c r="I18" t="n">
-        <v>0.502</v>
+        <v>-1.9038</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7044</v>
+        <v>1.5924</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2017</v>
+        <v>1.4452</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5027</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5912</v>
+        <v>-3.0809</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5904</v>
+        <v>-1.0299</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0008</v>
+        <v>-2.051</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1369</v>
+        <v>-0.4894</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0455</v>
+        <v>-0.2869</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0914</v>
+        <v>-0.2025</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.031</v>
+        <v>-0.8256</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0697</v>
+        <v>1.9902</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1007</v>
+        <v>-2.8158</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4884</v>
+        <v>-1.7183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4154</v>
+        <v>0.0048</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9038</v>
+        <v>-1.7231</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5924</v>
+        <v>1.2625</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4452</v>
+        <v>0.9312</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1472</v>
+        <v>0.3312</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0809</v>
+        <v>-2.9808</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0299</v>
+        <v>-0.9265</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.051</v>
+        <v>-2.0543</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7925</v>
+        <v>1.4134</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>0.7277</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2697</v>
+        <v>0.6858</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7905</v>
+        <v>-1.7512</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8365</v>
+        <v>-0.9545</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9539</v>
+        <v>-0.7967</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6544</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7196</v>
+        <v>0.7589</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5272</v>
+        <v>0.4092</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1924</v>
+        <v>0.3497</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. SHAHRVIN</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8015</v>
+        <v>-2.0248</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1061</v>
+        <v>0.2383</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6954</v>
+        <v>-2.2631</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2983</v>
+        <v>-4.1912</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9135</v>
+        <v>-2.1802</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3848</v>
+        <v>-2.011</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5191</v>
+        <v>-0.3203</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5559</v>
+        <v>-0.6246</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0368</v>
+        <v>0.3044</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7792</v>
+        <v>-3.8709</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3577</v>
+        <v>-1.5556</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4216</v>
+        <v>-2.3153</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7108</v>
+        <v>0.5427</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4129</v>
+        <v>0.5586</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2978</v>
+        <v>-0.0158</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>E. SHAHRVIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1985</v>
+        <v>-2.357</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3562</v>
+        <v>-1.46</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5547</v>
+        <v>-0.897</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1912</v>
+        <v>-2.2983</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1802</v>
+        <v>-1.9135</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.011</v>
+        <v>-0.3848</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3203</v>
+        <v>-1.5191</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6246</v>
+        <v>-1.5559</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3044</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.8709</v>
+        <v>-0.7792</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5556</v>
+        <v>-0.3577</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3153</v>
+        <v>-0.4216</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.369</v>
+        <v>0.1553</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6765</v>
+        <v>0.0591</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3075</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8576</v>
+        <v>-3.5551</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1498</v>
+        <v>-1.2061</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7078</v>
+        <v>-2.3489</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7115</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0174</v>
+        <v>0.2851</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9709</v>
+        <v>-0.0272</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0466</v>
+        <v>0.3123</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0412</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7505</v>
+        <v>-5.5452</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-3.2589</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9123</v>
+        <v>-2.2863</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3192</v>
+        <v>-3.8836</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0578</v>
+        <v>-2.3445</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2614</v>
+        <v>-1.5392</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8794999999999999</v>
+        <v>-2.2214</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1744</v>
+        <v>-1.4719</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0539</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.1987</v>
+        <v>-1.6622</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8834</v>
+        <v>-0.8726</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.3153</v>
+        <v>-0.7896</v>
       </c>
       <c r="P24" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>0.391</v>
+        <v>-0.2673</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6018</v>
+        <v>-0.0196</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2109</v>
+        <v>-0.2478</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.3584</v>
+        <v>-0.9304</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.3584</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0335</v>
+        <v>-6.1172</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6128</v>
+        <v>-1.8221</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4207</v>
+        <v>-4.295</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.8836</v>
+        <v>-2.7532</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.3445</v>
+        <v>-0.1668</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5392</v>
+        <v>-2.5864</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.2214</v>
+        <v>-0.2694</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4719</v>
+        <v>0.3697</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.6391</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6622</v>
+        <v>-2.4838</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8726</v>
+        <v>-0.5365</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7896</v>
+        <v>-1.9473</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7556</v>
+        <v>-0.3793</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3734</v>
+        <v>-0.393</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3822</v>
+        <v>0.0136</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9304</v>
+        <v>-3.2166</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0722</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.5382</v>
+        <v>-6.5089</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.176</v>
+        <v>-1.6638</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.3622</v>
+        <v>-4.8451</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.7532</v>
+        <v>-2.3192</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1668</v>
+        <v>-1.0578</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.5864</v>
+        <v>-1.2614</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2694</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3697</v>
+        <v>-0.1744</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6391</v>
+        <v>1.0539</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4838</v>
+        <v>-3.1987</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5365</v>
+        <v>-0.8834</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.9473</v>
+        <v>-2.3153</v>
       </c>
       <c r="P26" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8004</v>
+        <v>-0.3675</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7468</v>
+        <v>-0.2238</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0536</v>
+        <v>-0.1436</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.2166</v>
+        <v>-3.3584</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.2166</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="27">
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-23.8066</v>
+        <v>-23.0203</v>
       </c>
       <c r="E27" t="n">
-        <v>3.860200000000001</v>
+        <v>3.860399999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-27.6667</v>
+        <v>-26.8805</v>
       </c>
       <c r="G27" t="n">
         <v>-15.6894</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.8095</v>
+        <v>-7.809500000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-7.879899999999999</v>
@@ -2536,7 +2536,7 @@
         <v>18.5151</v>
       </c>
       <c r="K27" t="n">
-        <v>3.760400000000001</v>
+        <v>3.7604</v>
       </c>
       <c r="L27" t="n">
         <v>14.7547</v>
@@ -2551,7 +2551,7 @@
         <v>-22.6344</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0001000000000000167</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q27" t="n">
         <v>-17.3965</v>
@@ -2560,13 +2560,13 @@
         <v>17.3966</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5711999999999993</v>
+        <v>1.3573</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1404999999999995</v>
+        <v>0.1405</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4304</v>
+        <v>1.2169</v>
       </c>
       <c r="V27" t="n">
         <v>-8.6884</v>
